--- a/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N35_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T0801_W0022F0001T0006Z000C1N35_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>17.16263705202977</v>
+        <v>2.788928520954838</v>
       </c>
       <c r="D2" t="n">
-        <v>16.31530538723023</v>
+        <v>2.651237125424913</v>
       </c>
       <c r="E2" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F2" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>62.01070021154651</v>
+        <v>10.07673878437631</v>
       </c>
       <c r="D3" t="n">
-        <v>30.86605806412129</v>
+        <v>5.01573443541971</v>
       </c>
       <c r="E3" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F3" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>74.75204367970602</v>
+        <v>12.14720709795223</v>
       </c>
       <c r="D4" t="n">
-        <v>66.11785201861564</v>
+        <v>10.74415095302504</v>
       </c>
       <c r="E4" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F4" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>57.2125589443237</v>
+        <v>9.297040828452602</v>
       </c>
       <c r="D5" t="n">
-        <v>17.76328686566569</v>
+        <v>2.886534115670675</v>
       </c>
       <c r="E5" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F5" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>70.09422188513103</v>
+        <v>11.39031105633379</v>
       </c>
       <c r="D6" t="n">
-        <v>47.36213574177613</v>
+        <v>7.696347058038621</v>
       </c>
       <c r="E6" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F6" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>70.83216646607234</v>
+        <v>11.51022705073676</v>
       </c>
       <c r="D7" t="n">
-        <v>48.55288115133179</v>
+        <v>7.889843187091416</v>
       </c>
       <c r="E7" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F7" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>72.61416543733273</v>
+        <v>11.79980188356657</v>
       </c>
       <c r="D8" t="n">
-        <v>19.00657780874821</v>
+        <v>3.088568893921584</v>
       </c>
       <c r="E8" t="n">
-        <v>18.66889932901914</v>
+        <v>3.03369614096561</v>
       </c>
       <c r="F8" t="n">
-        <v>17.82368598261823</v>
+        <v>2.896348972175462</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
